--- a/data/showcase.xlsx
+++ b/data/showcase.xlsx
@@ -581,13 +581,13 @@
         <v>Shala Students Singing</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Hich Amuchi Prathana by Sankalp Marathi Students (Boston, MA)</v>
       </c>
       <c r="D7" t="str">
         <v>Competition</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>https://www.youtube.com/watch?v=OPvEpJOhSpY</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -596,10 +596,10 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/showcase.xlsx
+++ b/data/showcase.xlsx
@@ -509,7 +509,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I4" t="str">
         <v>99</v>

--- a/data/showcase.xlsx
+++ b/data/showcase.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -602,9 +602,38 @@
         <v>3</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>Maharashtra Day Shala Students Song</v>
+      </c>
+      <c r="C8" t="str">
+        <v>वेडात मराठे वीर दौडले सात Cover Song by Sankalp Marathi Shaala ( Boston, USA)</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>https://www.youtube.com/watch?v=nsKsCv8_FU4</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I8" t="str">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/showcase.xlsx
+++ b/data/showcase.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,9 +631,38 @@
         <v>4</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>Deepostav 2023</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Sankalp Marathi Deepotsav 2023 - Mangalagaur मंगळागौर</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>https://www.youtube.com/watch?v=NOuluNDWpwM</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/showcase.xlsx
+++ b/data/showcase.xlsx
@@ -654,10 +654,10 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
